--- a/01_測試站表單.xlsx
+++ b/01_測試站表單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\BetterGoogleForm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B9F58C2-2494-4CA0-ADEB-9AC87397EEA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA88DE04-8FA3-48C6-B11F-D143406DFE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{173906A5-8A09-4292-B53B-00E76CF0A74D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="194" xr2:uid="{173906A5-8A09-4292-B53B-00E76CF0A74D}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -101,9 +101,6 @@
     <t>廖彥凱</t>
   </si>
   <si>
-    <t>水果小瑪莉、Lucky Fruit Spin</t>
-  </si>
-  <si>
     <t>https://game.apex-win.com/h5_game/cocos/game1001/</t>
   </si>
   <si>
@@ -117,13 +114,17 @@
   </si>
   <si>
     <t>1/17/2025</t>
+  </si>
+  <si>
+    <t>水果小瑪莉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -153,6 +154,13 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="3">
@@ -201,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -222,6 +230,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -651,27 +662,27 @@
         <v>19</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="M2" s="4"/>
       <c r="N2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>

--- a/01_測試站表單.xlsx
+++ b/01_測試站表單.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\BetterGoogleForm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA88DE04-8FA3-48C6-B11F-D143406DFE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D8854B-5E8B-419D-98B8-CF34860E7B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="194" xr2:uid="{173906A5-8A09-4292-B53B-00E76CF0A74D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>Timestamp</t>
   </si>
@@ -118,6 +118,63 @@
   <si>
     <t>水果小瑪莉</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/10/2026 10:16:01</t>
+  </si>
+  <si>
+    <t>總部</t>
+  </si>
+  <si>
+    <t>黃昕穎</t>
+  </si>
+  <si>
+    <t>梅杜莎 蛇髮美人、Medusa The Serpent Queen</t>
+  </si>
+  <si>
+    <t>老虎機</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1UaWcDyW_BEUviM0_F5dcL5RmV3pLeIhP</t>
+  </si>
+  <si>
+    <t>特殊盤面 SLOT</t>
+  </si>
+  <si>
+    <t>https://testgame.apex-win.com/h5_game/cocos/game1044/</t>
+  </si>
+  <si>
+    <t>https://testgame.vmwrlx.link/h5_game/FTG/game1044/</t>
+  </si>
+  <si>
+    <t>https://dev-gamerecord.apex-win.com/#/game-detail?gamecode=game1044&amp;</t>
+  </si>
+  <si>
+    <t>https://gamerecord.vmwrlx.link/#/game-detail?gamecode=game1044&amp;</t>
+  </si>
+  <si>
+    <t>台灣站(1), 官網(3)</t>
+  </si>
+  <si>
+    <t>FREE GAME：×100、×200</t>
+  </si>
+  <si>
+    <t>4/17/2026</t>
+  </si>
+  <si>
+    <t>4/15/2026</t>
+  </si>
+  <si>
+    <t>機台內JP</t>
+  </si>
+  <si>
+    <t>重新送單，測掉FTG與越南站設定</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>未上傳</t>
   </si>
 </sst>
 </file>
@@ -209,10 +266,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -232,6 +292,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -569,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6BC270-E34E-4991-85B4-F6899CF61ADA}">
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -583,127 +649,205 @@
     <col min="12" max="12" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="2" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:33" s="3" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
     </row>
-    <row r="2" spans="1:28" s="6" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:33" s="7" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="5"/>
+      <c r="E2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="3" t="s">
+      <c r="M2" s="5"/>
+      <c r="N2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="5"/>
+    </row>
+    <row r="3" spans="1:33" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{2EAC5823-63D2-415B-A5CF-EF490AE46F72}"/>
     <hyperlink ref="H2" r:id="rId2" display="https://game.apex-win.com/h5_game/game_record/record1001/" xr:uid="{2E2C8BA9-89A7-4848-9AE5-F1211FBF5511}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{748B3B85-05DD-4B43-8BDC-EBA7BB4250EA}"/>
+    <hyperlink ref="H3" r:id="rId4" xr:uid="{7473FCE0-77A2-4CB2-9E7B-05677E1B39F5}"/>
+    <hyperlink ref="I3" r:id="rId5" xr:uid="{7F079677-B89B-4C48-B397-2BE3E7035C9E}"/>
+    <hyperlink ref="J3" r:id="rId6" location="/game-detail?gamecode=game1044&amp;" display="https://dev-gamerecord.apex-win.com/ - /game-detail?gamecode=game1044&amp;" xr:uid="{111236B3-8B4C-4254-AFF0-C0A0226297E8}"/>
+    <hyperlink ref="K3" r:id="rId7" location="/game-detail?gamecode=game1044&amp;" display="https://gamerecord.vmwrlx.link/ - /game-detail?gamecode=game1044&amp;" xr:uid="{0857BC84-39F9-4EB1-9554-AE7F2F3742CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
